--- a/excel/universities/university-of-oulu.xlsx
+++ b/excel/universities/university-of-oulu.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.oulu.fi/en/apply</t>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/applying-masters-programmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,27 +125,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill program-specific information here</t>
+          <t xml:space="preserve">University of Oulu publishes a central deadlines page and a central application-documents page for master's admissions.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -229,37 +229,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.oulu.fi/en/apply</t>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/applying-masters-programmes/deadlines</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify annual deadlines</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; graduating applicants submit final verified documents by 2026-07-31.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -275,7 +275,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -333,12 +333,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">International master's programmes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Proof of language skills</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -348,15 +348,225 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Language proof must be attached during the application period.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.oulu.fi/en/apply</t>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copy of transcript required for all applicants.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copy required if degree already completed.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official translations</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If needed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required if original documents are not in Finnish Swedish or English.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passport or identity card</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identification document must be attached to the application.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific attachments</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Examples include motivation letter GMAT GRE CV ACT SAT or video depending on programme.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -369,7 +579,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,15 +630,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -442,55 +667,147 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Harri Oinas-Kukkonen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">Professor and Dean</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
+          <t xml:space="preserve">Information systems science; Computer-human interaction; Persuasive design; Digital interventions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Harri_Oinas-Kukkonen</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?hl=en&amp;oi=ao&amp;user=CBDr26wAAAAJ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu researcher profile</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/researchers/harri-oinas-kukkonen</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harri.oinas-kukkonen@oulu.fi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu profile exposes both Google Scholar and ResearchGate links directly.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biomimetics and Intelligent Systems Group</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heli Koskimaki</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adj. Prof.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine learning; Data mining; Sensor fusion; Streaming data analysis; Wearable ICT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.oulu.fi/en</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu researcher profile</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/researchers/heli-koskimaki</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heli.koskimaki@oulu.fi</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official profile confirms both Google Scholar and ResearchGate profile links but their exact public URLs were not fetched automatically here.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>

--- a/excel/universities/university-of-oulu.xlsx
+++ b/excel/universities/university-of-oulu.xlsx
@@ -20,7 +20,8 @@
     <sheet name="UniversityInfo" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -579,6 +580,721 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parent_unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campus_or_city</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus_areas</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Biochemistry and Molecular Medicine</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biochemistry; Molecular medicine</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education and Psychology</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education; Psychology</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanities</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information technology; Electrical engineering</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centre for Wireless Communications</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wireless communications; 6G</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/centre-wireless-communications</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science; Engineering</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/computer-science-and-engineering</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microelectronics Research Unit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microelectronics</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/microelectronics-research-unit</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Medicine</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu Business School</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu Mining School</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mining</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technology</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial Engineering and Management</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial engineering; Management</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/industrial-engineering-and-management</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water, Energy and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water; Energy; Environmental engineering</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/water-energy-and-environmental-engineering</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
